--- a/results/Int All Data -1.0/Rando_5_permute.xlsx
+++ b/results/Int All Data -1.0/Rando_5_permute.xlsx
@@ -440,57 +440,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7996682471794323</v>
+        <v>0.8178703059756334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7990065717045042</v>
+        <v>0.8188184728530039</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7976670308228145</v>
+        <v>0.8193752657260551</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7996158058784939</v>
+        <v>0.8220691296011082</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.799931861504284</v>
+        <v>0.8132572312682489</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8005639727558642</v>
+        <v>0.8132572312682489</v>
       </c>
     </row>
     <row r="8">
@@ -500,1307 +500,1307 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7996010237668199</v>
+        <v>0.8148980456640547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8050116285945168</v>
+        <v>0.801849664516456</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8050116285945168</v>
+        <v>0.8003971460669728</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8158476203615845</v>
+        <v>0.8020527425744526</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8203853766904401</v>
+        <v>0.8016465864584594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.833975768599416</v>
+        <v>0.7966945790476941</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8352252089909027</v>
+        <v>0.7969581933725458</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8348567120641741</v>
+        <v>0.8013453129443432</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8340443998321878</v>
+        <v>0.800788520071292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8244201892673422</v>
+        <v>0.7976427459250646</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8248411274950093</v>
+        <v>0.7953912895351096</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8225910789252138</v>
+        <v>0.8014568826919775</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.80853258681323</v>
+        <v>0.7979049524297568</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8088109832497558</v>
+        <v>0.8040754281885014</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8108579537615547</v>
+        <v>0.804113087377766</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8155382518815517</v>
+        <v>0.7984765274144819</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8155382518815517</v>
+        <v>0.8075749171497837</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8155382518815517</v>
+        <v>0.8061223987003004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8107449761937611</v>
+        <v>0.8065890910831487</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8121746175656537</v>
+        <v>0.7769242085938974</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8136419181268109</v>
+        <v>0.7766458121573718</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8145753028925073</v>
+        <v>0.7902967403332029</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.804942997361745</v>
+        <v>0.7840886053851936</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8030466636070042</v>
+        <v>0.7983258906574238</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.807885693449976</v>
+        <v>0.7947363012059387</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8072535821983957</v>
+        <v>0.7845996441030636</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8072535821983957</v>
+        <v>0.7914546724143271</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8086455643810238</v>
+        <v>0.7977757849301299</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8081869669640922</v>
+        <v>0.7935393021153906</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7923303365534873</v>
+        <v>0.7935393021153906</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8025799712241559</v>
+        <v>0.7894305789801188</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8030991049079426</v>
+        <v>0.7914103260793053</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8080887715079725</v>
+        <v>0.7938419834496662</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8068622081940764</v>
+        <v>0.8000124592084109</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8136957672479087</v>
+        <v>0.805084131332727</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8141019233639017</v>
+        <v>0.8093086476761113</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.822011408974572</v>
+        <v>0.8095279156659412</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.822011408974572</v>
+        <v>0.8066080966553009</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8217706717273109</v>
+        <v>0.8079624196486643</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8192570088326636</v>
+        <v>0.8193471093228666</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8025894740102321</v>
+        <v>0.8187903164498154</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8019587705788112</v>
+        <v>0.8196255057593922</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7945927035496778</v>
+        <v>0.8102406246216484</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.800070531789987</v>
+        <v>0.8114295287462798</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8102582223736411</v>
+        <v>0.8158314304297511</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.825549964945278</v>
+        <v>0.8121073941530412</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8258660205710682</v>
+        <v>0.8075548557125118</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8320350885096535</v>
+        <v>0.8075925149017764</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8273709803214898</v>
+        <v>0.8075925149017764</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8239172455153889</v>
+        <v>0.8040634617171464</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8197412989675047</v>
+        <v>0.7991343313839717</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8189437688471923</v>
+        <v>0.7912019686957109</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8190715285266599</v>
+        <v>0.7896445676443509</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8101948704664671</v>
+        <v>0.793971150949293</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7982519800990542</v>
+        <v>0.7917425716369288</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7982519800990542</v>
+        <v>0.7913511976326095</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7992001469764247</v>
+        <v>0.7846992473793428</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7925334146114839</v>
+        <v>0.7929853248826582</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7933013805084483</v>
+        <v>0.7905321982548661</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7654737033272422</v>
+        <v>0.7861975199840072</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7684163994154731</v>
+        <v>0.7861975199840072</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7669195346309681</v>
+        <v>0.7862351791732718</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7706974200287758</v>
+        <v>0.7808164793796581</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.758369842802801</v>
+        <v>0.7509351445408958</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7640669390329402</v>
+        <v>0.7506190889151056</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7660009319769455</v>
+        <v>0.7479776663409909</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7643372405035491</v>
+        <v>0.7481511801756396</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7643372405035491</v>
+        <v>0.7452918974318545</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7624032475595437</v>
+        <v>0.7386547292902615</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7624032475595437</v>
+        <v>0.7347867434022508</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7377804729712607</v>
+        <v>0.738307701620964</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7372236800982095</v>
+        <v>0.7421756875089749</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7320914717070383</v>
+        <v>0.7412275206316044</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.730548852767352</v>
+        <v>0.7455245397131989</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7611914663573216</v>
+        <v>0.7458782545282536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7524320093254007</v>
+        <v>0.7392329914207439</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7490064309224882</v>
+        <v>0.7622297337248951</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7480582640451179</v>
+        <v>0.7570369890668687</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7497810839652099</v>
+        <v>0.7570369890668687</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7574565194743763</v>
+        <v>0.751762238884556</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6421539366875118</v>
+        <v>0.7553356384042077</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6142414383417005</v>
+        <v>0.7674735118637005</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6085147778882134</v>
+        <v>0.7356581840809328</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6088308335140036</v>
+        <v>0.7362526361432484</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6063924889978854</v>
+        <v>0.7097025557567174</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6057980369355697</v>
+        <v>0.7087086347241658</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6289682930743695</v>
+        <v>0.7064504911884536</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6483525688494449</v>
+        <v>0.6061679416824577</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6482772504709159</v>
+        <v>0.6061679416824577</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6032910611866797</v>
+        <v>0.6068377121233025</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6050596352619531</v>
+        <v>0.6043631162380793</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6056917465135334</v>
+        <v>0.6046791718638694</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6056917465135334</v>
+        <v>0.565352419620508</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5749885966567087</v>
+        <v>0.567640127379568</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5650025763108918</v>
+        <v>0.5756921547813796</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5965556975889672</v>
+        <v>0.56904689167387</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.590437663131161</v>
+        <v>0.5646745542137466</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6070608516185708</v>
+        <v>0.5531082557389789</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6088442078055181</v>
+        <v>0.5531082557389789</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.617693765327642</v>
+        <v>0.5537027078012946</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6170993132653262</v>
+        <v>0.5806656314495761</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6252791003466053</v>
+        <v>0.5806656314495761</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6320440281676658</v>
+        <v>0.5783779236905161</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6334669823938011</v>
+        <v>0.5800416151639125</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6266267361942116</v>
+        <v>0.5866034649269763</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.588700061099395</v>
+        <v>0.5782501640110486</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.574710200220183</v>
+        <v>0.5741185637981862</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5322228917189202</v>
+        <v>0.5895757252385552</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5322228917189202</v>
+        <v>0.5895757252385552</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5452040494539065</v>
+        <v>0.5579849447712152</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5410576671293702</v>
+        <v>0.5741414408757768</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5557845218620392</v>
+        <v>0.5729525367511453</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5604352557586884</v>
+        <v>0.5698739860175301</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5523079099783477</v>
+        <v>0.5719667106845103</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5387027359576978</v>
+        <v>0.5626800250028861</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5395379252672747</v>
+        <v>0.5626800250028861</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5670953009778719</v>
+        <v>0.5625751424010091</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5908480427076324</v>
+        <v>0.5447025135221126</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5902159314560521</v>
+        <v>0.5447025135221126</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5815856419237581</v>
+        <v>0.5488112366573844</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5901043617084178</v>
+        <v>0.5441309385373875</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5790343198398464</v>
+        <v>0.5466446014320346</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5773558462547761</v>
+        <v>0.5501064312040522</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5707939964917121</v>
+        <v>0.552682038185714</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5672110941859843</v>
+        <v>0.544601854380714</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5753021885972198</v>
+        <v>0.5581478999546682</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5717879175242637</v>
+        <v>0.5549201202841545</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5880978660262024</v>
+        <v>0.5549201202841545</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5880978660262024</v>
+        <v>0.5549201202841545</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.546609757883089</v>
+        <v>0.5560337060302569</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5357603918245067</v>
+        <v>0.5425401017572411</v>
       </c>
     </row>
     <row r="139">
@@ -1810,177 +1810,177 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5309308647676111</v>
+        <v>0.5424271241894476</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5366561174009388</v>
+        <v>0.531588316782061</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5369721730267288</v>
+        <v>0.5297444243282586</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5373716419969647</v>
+        <v>0.5357399784321952</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5439187096483546</v>
+        <v>0.5395850872426152</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4602209855304244</v>
+        <v>0.5499557944469942</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4676394938604962</v>
+        <v>0.542710799951571</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4676394938604962</v>
+        <v>0.5309104513752995</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4692479283926354</v>
+        <v>0.51723136679628</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4659662996010238</v>
+        <v>0.5164338366759677</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5029916178387708</v>
+        <v>0.5000376591892646</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4845878888047325</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4950564395101912</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4615429286601213</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4646725128745154</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4646725128745154</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5020230375690887</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5025273891412015</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
